--- a/templates/SunoOriginalStudio批量原创模板_v0.5.8.xlsx
+++ b/templates/SunoOriginalStudio批量原创模板_v0.5.8.xlsx
@@ -1,3 +1,111 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批量原创" sheetId="1" r:id="R4ec6391bfadd4e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R515d5386a6d44041"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="2">
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="4">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="2">
+    <x:border/>
+    <x:border/>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="20">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+</x:styleSheet>
+</file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BatchSongsTable" displayName="BatchSongsTable" ref="A1:K102" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
@@ -30,6 +138,1609 @@
 </x:table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+  <a:themeElements>
+    <a:clrScheme name="ChatGPT">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="ChatGPT">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>歌名</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>歌词</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>风格</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>排除风格</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>模型</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>人声</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Weirdness</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>风格影响</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>账号</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>提交间隔秒</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="18" t="str">
+        <x:v>凌晨以后没有你的城市</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="str">
+        <x:v>[Verse]
+第一段歌词……
+[Chorus]
+副歌歌词……</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="str">
+        <x:v>sad piano pop, cinematic, intimate vocal</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>rap, metal, spoken word</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="str">
+        <x:v>v5.5</x:v>
+      </x:c>
+      <x:c r="F2" s="18" t="str">
+        <x:v>女声</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H2" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I2" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="18" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K2" s="18" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="15" t="str"/>
+      <x:c r="B3" s="15" t="str"/>
+      <x:c r="C3" s="15" t="str"/>
+      <x:c r="D3" s="15" t="str"/>
+      <x:c r="E3" s="15" t="str"/>
+      <x:c r="F3" s="15" t="str"/>
+      <x:c r="G3" s="15" t="str"/>
+      <x:c r="H3" s="15" t="str"/>
+      <x:c r="I3" s="15" t="str"/>
+      <x:c r="J3" s="15" t="str"/>
+      <x:c r="K3" s="15" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="15" t="str"/>
+      <x:c r="B4" s="15" t="str"/>
+      <x:c r="C4" s="15" t="str"/>
+      <x:c r="D4" s="15" t="str"/>
+      <x:c r="E4" s="15" t="str"/>
+      <x:c r="F4" s="15" t="str"/>
+      <x:c r="G4" s="15" t="str"/>
+      <x:c r="H4" s="15" t="str"/>
+      <x:c r="I4" s="15" t="str"/>
+      <x:c r="J4" s="15" t="str"/>
+      <x:c r="K4" s="15" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="15" t="str"/>
+      <x:c r="B5" s="15" t="str"/>
+      <x:c r="C5" s="15" t="str"/>
+      <x:c r="D5" s="15" t="str"/>
+      <x:c r="E5" s="15" t="str"/>
+      <x:c r="F5" s="15" t="str"/>
+      <x:c r="G5" s="15" t="str"/>
+      <x:c r="H5" s="15" t="str"/>
+      <x:c r="I5" s="15" t="str"/>
+      <x:c r="J5" s="15" t="str"/>
+      <x:c r="K5" s="15" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="15" t="str"/>
+      <x:c r="B6" s="15" t="str"/>
+      <x:c r="C6" s="15" t="str"/>
+      <x:c r="D6" s="15" t="str"/>
+      <x:c r="E6" s="15" t="str"/>
+      <x:c r="F6" s="15" t="str"/>
+      <x:c r="G6" s="15" t="str"/>
+      <x:c r="H6" s="15" t="str"/>
+      <x:c r="I6" s="15" t="str"/>
+      <x:c r="J6" s="15" t="str"/>
+      <x:c r="K6" s="15" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="15" t="str"/>
+      <x:c r="B7" s="15" t="str"/>
+      <x:c r="C7" s="15" t="str"/>
+      <x:c r="D7" s="15" t="str"/>
+      <x:c r="E7" s="15" t="str"/>
+      <x:c r="F7" s="15" t="str"/>
+      <x:c r="G7" s="15" t="str"/>
+      <x:c r="H7" s="15" t="str"/>
+      <x:c r="I7" s="15" t="str"/>
+      <x:c r="J7" s="15" t="str"/>
+      <x:c r="K7" s="15" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="15" t="str"/>
+      <x:c r="B8" s="15" t="str"/>
+      <x:c r="C8" s="15" t="str"/>
+      <x:c r="D8" s="15" t="str"/>
+      <x:c r="E8" s="15" t="str"/>
+      <x:c r="F8" s="15" t="str"/>
+      <x:c r="G8" s="15" t="str"/>
+      <x:c r="H8" s="15" t="str"/>
+      <x:c r="I8" s="15" t="str"/>
+      <x:c r="J8" s="15" t="str"/>
+      <x:c r="K8" s="15" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str"/>
+      <x:c r="B9" s="15" t="str"/>
+      <x:c r="C9" s="15" t="str"/>
+      <x:c r="D9" s="15" t="str"/>
+      <x:c r="E9" s="15" t="str"/>
+      <x:c r="F9" s="15" t="str"/>
+      <x:c r="G9" s="15" t="str"/>
+      <x:c r="H9" s="15" t="str"/>
+      <x:c r="I9" s="15" t="str"/>
+      <x:c r="J9" s="15" t="str"/>
+      <x:c r="K9" s="15" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="15" t="str"/>
+      <x:c r="B10" s="15" t="str"/>
+      <x:c r="C10" s="15" t="str"/>
+      <x:c r="D10" s="15" t="str"/>
+      <x:c r="E10" s="15" t="str"/>
+      <x:c r="F10" s="15" t="str"/>
+      <x:c r="G10" s="15" t="str"/>
+      <x:c r="H10" s="15" t="str"/>
+      <x:c r="I10" s="15" t="str"/>
+      <x:c r="J10" s="15" t="str"/>
+      <x:c r="K10" s="15" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="15" t="str"/>
+      <x:c r="B11" s="15" t="str"/>
+      <x:c r="C11" s="15" t="str"/>
+      <x:c r="D11" s="15" t="str"/>
+      <x:c r="E11" s="15" t="str"/>
+      <x:c r="F11" s="15" t="str"/>
+      <x:c r="G11" s="15" t="str"/>
+      <x:c r="H11" s="15" t="str"/>
+      <x:c r="I11" s="15" t="str"/>
+      <x:c r="J11" s="15" t="str"/>
+      <x:c r="K11" s="15" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="15" t="str"/>
+      <x:c r="B12" s="15" t="str"/>
+      <x:c r="C12" s="15" t="str"/>
+      <x:c r="D12" s="15" t="str"/>
+      <x:c r="E12" s="15" t="str"/>
+      <x:c r="F12" s="15" t="str"/>
+      <x:c r="G12" s="15" t="str"/>
+      <x:c r="H12" s="15" t="str"/>
+      <x:c r="I12" s="15" t="str"/>
+      <x:c r="J12" s="15" t="str"/>
+      <x:c r="K12" s="15" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="15" t="str"/>
+      <x:c r="B13" s="15" t="str"/>
+      <x:c r="C13" s="15" t="str"/>
+      <x:c r="D13" s="15" t="str"/>
+      <x:c r="E13" s="15" t="str"/>
+      <x:c r="F13" s="15" t="str"/>
+      <x:c r="G13" s="15" t="str"/>
+      <x:c r="H13" s="15" t="str"/>
+      <x:c r="I13" s="15" t="str"/>
+      <x:c r="J13" s="15" t="str"/>
+      <x:c r="K13" s="15" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="15" t="str"/>
+      <x:c r="B14" s="15" t="str"/>
+      <x:c r="C14" s="15" t="str"/>
+      <x:c r="D14" s="15" t="str"/>
+      <x:c r="E14" s="15" t="str"/>
+      <x:c r="F14" s="15" t="str"/>
+      <x:c r="G14" s="15" t="str"/>
+      <x:c r="H14" s="15" t="str"/>
+      <x:c r="I14" s="15" t="str"/>
+      <x:c r="J14" s="15" t="str"/>
+      <x:c r="K14" s="15" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="15" t="str"/>
+      <x:c r="B15" s="15" t="str"/>
+      <x:c r="C15" s="15" t="str"/>
+      <x:c r="D15" s="15" t="str"/>
+      <x:c r="E15" s="15" t="str"/>
+      <x:c r="F15" s="15" t="str"/>
+      <x:c r="G15" s="15" t="str"/>
+      <x:c r="H15" s="15" t="str"/>
+      <x:c r="I15" s="15" t="str"/>
+      <x:c r="J15" s="15" t="str"/>
+      <x:c r="K15" s="15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="15" t="str"/>
+      <x:c r="B16" s="15" t="str"/>
+      <x:c r="C16" s="15" t="str"/>
+      <x:c r="D16" s="15" t="str"/>
+      <x:c r="E16" s="15" t="str"/>
+      <x:c r="F16" s="15" t="str"/>
+      <x:c r="G16" s="15" t="str"/>
+      <x:c r="H16" s="15" t="str"/>
+      <x:c r="I16" s="15" t="str"/>
+      <x:c r="J16" s="15" t="str"/>
+      <x:c r="K16" s="15" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="15" t="str"/>
+      <x:c r="B17" s="15" t="str"/>
+      <x:c r="C17" s="15" t="str"/>
+      <x:c r="D17" s="15" t="str"/>
+      <x:c r="E17" s="15" t="str"/>
+      <x:c r="F17" s="15" t="str"/>
+      <x:c r="G17" s="15" t="str"/>
+      <x:c r="H17" s="15" t="str"/>
+      <x:c r="I17" s="15" t="str"/>
+      <x:c r="J17" s="15" t="str"/>
+      <x:c r="K17" s="15" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="15" t="str"/>
+      <x:c r="B18" s="15" t="str"/>
+      <x:c r="C18" s="15" t="str"/>
+      <x:c r="D18" s="15" t="str"/>
+      <x:c r="E18" s="15" t="str"/>
+      <x:c r="F18" s="15" t="str"/>
+      <x:c r="G18" s="15" t="str"/>
+      <x:c r="H18" s="15" t="str"/>
+      <x:c r="I18" s="15" t="str"/>
+      <x:c r="J18" s="15" t="str"/>
+      <x:c r="K18" s="15" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="15" t="str"/>
+      <x:c r="B19" s="15" t="str"/>
+      <x:c r="C19" s="15" t="str"/>
+      <x:c r="D19" s="15" t="str"/>
+      <x:c r="E19" s="15" t="str"/>
+      <x:c r="F19" s="15" t="str"/>
+      <x:c r="G19" s="15" t="str"/>
+      <x:c r="H19" s="15" t="str"/>
+      <x:c r="I19" s="15" t="str"/>
+      <x:c r="J19" s="15" t="str"/>
+      <x:c r="K19" s="15" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="15" t="str"/>
+      <x:c r="B20" s="15" t="str"/>
+      <x:c r="C20" s="15" t="str"/>
+      <x:c r="D20" s="15" t="str"/>
+      <x:c r="E20" s="15" t="str"/>
+      <x:c r="F20" s="15" t="str"/>
+      <x:c r="G20" s="15" t="str"/>
+      <x:c r="H20" s="15" t="str"/>
+      <x:c r="I20" s="15" t="str"/>
+      <x:c r="J20" s="15" t="str"/>
+      <x:c r="K20" s="15" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="15" t="str"/>
+      <x:c r="B21" s="15" t="str"/>
+      <x:c r="C21" s="15" t="str"/>
+      <x:c r="D21" s="15" t="str"/>
+      <x:c r="E21" s="15" t="str"/>
+      <x:c r="F21" s="15" t="str"/>
+      <x:c r="G21" s="15" t="str"/>
+      <x:c r="H21" s="15" t="str"/>
+      <x:c r="I21" s="15" t="str"/>
+      <x:c r="J21" s="15" t="str"/>
+      <x:c r="K21" s="15" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="15" t="str"/>
+      <x:c r="B22" s="15" t="str"/>
+      <x:c r="C22" s="15" t="str"/>
+      <x:c r="D22" s="15" t="str"/>
+      <x:c r="E22" s="15" t="str"/>
+      <x:c r="F22" s="15" t="str"/>
+      <x:c r="G22" s="15" t="str"/>
+      <x:c r="H22" s="15" t="str"/>
+      <x:c r="I22" s="15" t="str"/>
+      <x:c r="J22" s="15" t="str"/>
+      <x:c r="K22" s="15" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="15" t="str"/>
+      <x:c r="B23" s="15" t="str"/>
+      <x:c r="C23" s="15" t="str"/>
+      <x:c r="D23" s="15" t="str"/>
+      <x:c r="E23" s="15" t="str"/>
+      <x:c r="F23" s="15" t="str"/>
+      <x:c r="G23" s="15" t="str"/>
+      <x:c r="H23" s="15" t="str"/>
+      <x:c r="I23" s="15" t="str"/>
+      <x:c r="J23" s="15" t="str"/>
+      <x:c r="K23" s="15" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="15" t="str"/>
+      <x:c r="B24" s="15" t="str"/>
+      <x:c r="C24" s="15" t="str"/>
+      <x:c r="D24" s="15" t="str"/>
+      <x:c r="E24" s="15" t="str"/>
+      <x:c r="F24" s="15" t="str"/>
+      <x:c r="G24" s="15" t="str"/>
+      <x:c r="H24" s="15" t="str"/>
+      <x:c r="I24" s="15" t="str"/>
+      <x:c r="J24" s="15" t="str"/>
+      <x:c r="K24" s="15" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="15" t="str"/>
+      <x:c r="B25" s="15" t="str"/>
+      <x:c r="C25" s="15" t="str"/>
+      <x:c r="D25" s="15" t="str"/>
+      <x:c r="E25" s="15" t="str"/>
+      <x:c r="F25" s="15" t="str"/>
+      <x:c r="G25" s="15" t="str"/>
+      <x:c r="H25" s="15" t="str"/>
+      <x:c r="I25" s="15" t="str"/>
+      <x:c r="J25" s="15" t="str"/>
+      <x:c r="K25" s="15" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="15" t="str"/>
+      <x:c r="B26" s="15" t="str"/>
+      <x:c r="C26" s="15" t="str"/>
+      <x:c r="D26" s="15" t="str"/>
+      <x:c r="E26" s="15" t="str"/>
+      <x:c r="F26" s="15" t="str"/>
+      <x:c r="G26" s="15" t="str"/>
+      <x:c r="H26" s="15" t="str"/>
+      <x:c r="I26" s="15" t="str"/>
+      <x:c r="J26" s="15" t="str"/>
+      <x:c r="K26" s="15" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="15" t="str"/>
+      <x:c r="B27" s="15" t="str"/>
+      <x:c r="C27" s="15" t="str"/>
+      <x:c r="D27" s="15" t="str"/>
+      <x:c r="E27" s="15" t="str"/>
+      <x:c r="F27" s="15" t="str"/>
+      <x:c r="G27" s="15" t="str"/>
+      <x:c r="H27" s="15" t="str"/>
+      <x:c r="I27" s="15" t="str"/>
+      <x:c r="J27" s="15" t="str"/>
+      <x:c r="K27" s="15" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="15" t="str"/>
+      <x:c r="B28" s="15" t="str"/>
+      <x:c r="C28" s="15" t="str"/>
+      <x:c r="D28" s="15" t="str"/>
+      <x:c r="E28" s="15" t="str"/>
+      <x:c r="F28" s="15" t="str"/>
+      <x:c r="G28" s="15" t="str"/>
+      <x:c r="H28" s="15" t="str"/>
+      <x:c r="I28" s="15" t="str"/>
+      <x:c r="J28" s="15" t="str"/>
+      <x:c r="K28" s="15" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="15" t="str"/>
+      <x:c r="B29" s="15" t="str"/>
+      <x:c r="C29" s="15" t="str"/>
+      <x:c r="D29" s="15" t="str"/>
+      <x:c r="E29" s="15" t="str"/>
+      <x:c r="F29" s="15" t="str"/>
+      <x:c r="G29" s="15" t="str"/>
+      <x:c r="H29" s="15" t="str"/>
+      <x:c r="I29" s="15" t="str"/>
+      <x:c r="J29" s="15" t="str"/>
+      <x:c r="K29" s="15" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="15" t="str"/>
+      <x:c r="B30" s="15" t="str"/>
+      <x:c r="C30" s="15" t="str"/>
+      <x:c r="D30" s="15" t="str"/>
+      <x:c r="E30" s="15" t="str"/>
+      <x:c r="F30" s="15" t="str"/>
+      <x:c r="G30" s="15" t="str"/>
+      <x:c r="H30" s="15" t="str"/>
+      <x:c r="I30" s="15" t="str"/>
+      <x:c r="J30" s="15" t="str"/>
+      <x:c r="K30" s="15" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="15" t="str"/>
+      <x:c r="B31" s="15" t="str"/>
+      <x:c r="C31" s="15" t="str"/>
+      <x:c r="D31" s="15" t="str"/>
+      <x:c r="E31" s="15" t="str"/>
+      <x:c r="F31" s="15" t="str"/>
+      <x:c r="G31" s="15" t="str"/>
+      <x:c r="H31" s="15" t="str"/>
+      <x:c r="I31" s="15" t="str"/>
+      <x:c r="J31" s="15" t="str"/>
+      <x:c r="K31" s="15" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="15" t="str"/>
+      <x:c r="B32" s="15" t="str"/>
+      <x:c r="C32" s="15" t="str"/>
+      <x:c r="D32" s="15" t="str"/>
+      <x:c r="E32" s="15" t="str"/>
+      <x:c r="F32" s="15" t="str"/>
+      <x:c r="G32" s="15" t="str"/>
+      <x:c r="H32" s="15" t="str"/>
+      <x:c r="I32" s="15" t="str"/>
+      <x:c r="J32" s="15" t="str"/>
+      <x:c r="K32" s="15" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="15" t="str"/>
+      <x:c r="B33" s="15" t="str"/>
+      <x:c r="C33" s="15" t="str"/>
+      <x:c r="D33" s="15" t="str"/>
+      <x:c r="E33" s="15" t="str"/>
+      <x:c r="F33" s="15" t="str"/>
+      <x:c r="G33" s="15" t="str"/>
+      <x:c r="H33" s="15" t="str"/>
+      <x:c r="I33" s="15" t="str"/>
+      <x:c r="J33" s="15" t="str"/>
+      <x:c r="K33" s="15" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="15" t="str"/>
+      <x:c r="B34" s="15" t="str"/>
+      <x:c r="C34" s="15" t="str"/>
+      <x:c r="D34" s="15" t="str"/>
+      <x:c r="E34" s="15" t="str"/>
+      <x:c r="F34" s="15" t="str"/>
+      <x:c r="G34" s="15" t="str"/>
+      <x:c r="H34" s="15" t="str"/>
+      <x:c r="I34" s="15" t="str"/>
+      <x:c r="J34" s="15" t="str"/>
+      <x:c r="K34" s="15" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="15" t="str"/>
+      <x:c r="B35" s="15" t="str"/>
+      <x:c r="C35" s="15" t="str"/>
+      <x:c r="D35" s="15" t="str"/>
+      <x:c r="E35" s="15" t="str"/>
+      <x:c r="F35" s="15" t="str"/>
+      <x:c r="G35" s="15" t="str"/>
+      <x:c r="H35" s="15" t="str"/>
+      <x:c r="I35" s="15" t="str"/>
+      <x:c r="J35" s="15" t="str"/>
+      <x:c r="K35" s="15" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="15" t="str"/>
+      <x:c r="B36" s="15" t="str"/>
+      <x:c r="C36" s="15" t="str"/>
+      <x:c r="D36" s="15" t="str"/>
+      <x:c r="E36" s="15" t="str"/>
+      <x:c r="F36" s="15" t="str"/>
+      <x:c r="G36" s="15" t="str"/>
+      <x:c r="H36" s="15" t="str"/>
+      <x:c r="I36" s="15" t="str"/>
+      <x:c r="J36" s="15" t="str"/>
+      <x:c r="K36" s="15" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="15" t="str"/>
+      <x:c r="B37" s="15" t="str"/>
+      <x:c r="C37" s="15" t="str"/>
+      <x:c r="D37" s="15" t="str"/>
+      <x:c r="E37" s="15" t="str"/>
+      <x:c r="F37" s="15" t="str"/>
+      <x:c r="G37" s="15" t="str"/>
+      <x:c r="H37" s="15" t="str"/>
+      <x:c r="I37" s="15" t="str"/>
+      <x:c r="J37" s="15" t="str"/>
+      <x:c r="K37" s="15" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="15" t="str"/>
+      <x:c r="B38" s="15" t="str"/>
+      <x:c r="C38" s="15" t="str"/>
+      <x:c r="D38" s="15" t="str"/>
+      <x:c r="E38" s="15" t="str"/>
+      <x:c r="F38" s="15" t="str"/>
+      <x:c r="G38" s="15" t="str"/>
+      <x:c r="H38" s="15" t="str"/>
+      <x:c r="I38" s="15" t="str"/>
+      <x:c r="J38" s="15" t="str"/>
+      <x:c r="K38" s="15" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="15" t="str"/>
+      <x:c r="B39" s="15" t="str"/>
+      <x:c r="C39" s="15" t="str"/>
+      <x:c r="D39" s="15" t="str"/>
+      <x:c r="E39" s="15" t="str"/>
+      <x:c r="F39" s="15" t="str"/>
+      <x:c r="G39" s="15" t="str"/>
+      <x:c r="H39" s="15" t="str"/>
+      <x:c r="I39" s="15" t="str"/>
+      <x:c r="J39" s="15" t="str"/>
+      <x:c r="K39" s="15" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="15" t="str"/>
+      <x:c r="B40" s="15" t="str"/>
+      <x:c r="C40" s="15" t="str"/>
+      <x:c r="D40" s="15" t="str"/>
+      <x:c r="E40" s="15" t="str"/>
+      <x:c r="F40" s="15" t="str"/>
+      <x:c r="G40" s="15" t="str"/>
+      <x:c r="H40" s="15" t="str"/>
+      <x:c r="I40" s="15" t="str"/>
+      <x:c r="J40" s="15" t="str"/>
+      <x:c r="K40" s="15" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="15" t="str"/>
+      <x:c r="B41" s="15" t="str"/>
+      <x:c r="C41" s="15" t="str"/>
+      <x:c r="D41" s="15" t="str"/>
+      <x:c r="E41" s="15" t="str"/>
+      <x:c r="F41" s="15" t="str"/>
+      <x:c r="G41" s="15" t="str"/>
+      <x:c r="H41" s="15" t="str"/>
+      <x:c r="I41" s="15" t="str"/>
+      <x:c r="J41" s="15" t="str"/>
+      <x:c r="K41" s="15" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="15" t="str"/>
+      <x:c r="B42" s="15" t="str"/>
+      <x:c r="C42" s="15" t="str"/>
+      <x:c r="D42" s="15" t="str"/>
+      <x:c r="E42" s="15" t="str"/>
+      <x:c r="F42" s="15" t="str"/>
+      <x:c r="G42" s="15" t="str"/>
+      <x:c r="H42" s="15" t="str"/>
+      <x:c r="I42" s="15" t="str"/>
+      <x:c r="J42" s="15" t="str"/>
+      <x:c r="K42" s="15" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="15" t="str"/>
+      <x:c r="B43" s="15" t="str"/>
+      <x:c r="C43" s="15" t="str"/>
+      <x:c r="D43" s="15" t="str"/>
+      <x:c r="E43" s="15" t="str"/>
+      <x:c r="F43" s="15" t="str"/>
+      <x:c r="G43" s="15" t="str"/>
+      <x:c r="H43" s="15" t="str"/>
+      <x:c r="I43" s="15" t="str"/>
+      <x:c r="J43" s="15" t="str"/>
+      <x:c r="K43" s="15" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="15" t="str"/>
+      <x:c r="B44" s="15" t="str"/>
+      <x:c r="C44" s="15" t="str"/>
+      <x:c r="D44" s="15" t="str"/>
+      <x:c r="E44" s="15" t="str"/>
+      <x:c r="F44" s="15" t="str"/>
+      <x:c r="G44" s="15" t="str"/>
+      <x:c r="H44" s="15" t="str"/>
+      <x:c r="I44" s="15" t="str"/>
+      <x:c r="J44" s="15" t="str"/>
+      <x:c r="K44" s="15" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="15" t="str"/>
+      <x:c r="B45" s="15" t="str"/>
+      <x:c r="C45" s="15" t="str"/>
+      <x:c r="D45" s="15" t="str"/>
+      <x:c r="E45" s="15" t="str"/>
+      <x:c r="F45" s="15" t="str"/>
+      <x:c r="G45" s="15" t="str"/>
+      <x:c r="H45" s="15" t="str"/>
+      <x:c r="I45" s="15" t="str"/>
+      <x:c r="J45" s="15" t="str"/>
+      <x:c r="K45" s="15" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="15" t="str"/>
+      <x:c r="B46" s="15" t="str"/>
+      <x:c r="C46" s="15" t="str"/>
+      <x:c r="D46" s="15" t="str"/>
+      <x:c r="E46" s="15" t="str"/>
+      <x:c r="F46" s="15" t="str"/>
+      <x:c r="G46" s="15" t="str"/>
+      <x:c r="H46" s="15" t="str"/>
+      <x:c r="I46" s="15" t="str"/>
+      <x:c r="J46" s="15" t="str"/>
+      <x:c r="K46" s="15" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="15" t="str"/>
+      <x:c r="B47" s="15" t="str"/>
+      <x:c r="C47" s="15" t="str"/>
+      <x:c r="D47" s="15" t="str"/>
+      <x:c r="E47" s="15" t="str"/>
+      <x:c r="F47" s="15" t="str"/>
+      <x:c r="G47" s="15" t="str"/>
+      <x:c r="H47" s="15" t="str"/>
+      <x:c r="I47" s="15" t="str"/>
+      <x:c r="J47" s="15" t="str"/>
+      <x:c r="K47" s="15" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="15" t="str"/>
+      <x:c r="B48" s="15" t="str"/>
+      <x:c r="C48" s="15" t="str"/>
+      <x:c r="D48" s="15" t="str"/>
+      <x:c r="E48" s="15" t="str"/>
+      <x:c r="F48" s="15" t="str"/>
+      <x:c r="G48" s="15" t="str"/>
+      <x:c r="H48" s="15" t="str"/>
+      <x:c r="I48" s="15" t="str"/>
+      <x:c r="J48" s="15" t="str"/>
+      <x:c r="K48" s="15" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="15" t="str"/>
+      <x:c r="B49" s="15" t="str"/>
+      <x:c r="C49" s="15" t="str"/>
+      <x:c r="D49" s="15" t="str"/>
+      <x:c r="E49" s="15" t="str"/>
+      <x:c r="F49" s="15" t="str"/>
+      <x:c r="G49" s="15" t="str"/>
+      <x:c r="H49" s="15" t="str"/>
+      <x:c r="I49" s="15" t="str"/>
+      <x:c r="J49" s="15" t="str"/>
+      <x:c r="K49" s="15" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="15" t="str"/>
+      <x:c r="B50" s="15" t="str"/>
+      <x:c r="C50" s="15" t="str"/>
+      <x:c r="D50" s="15" t="str"/>
+      <x:c r="E50" s="15" t="str"/>
+      <x:c r="F50" s="15" t="str"/>
+      <x:c r="G50" s="15" t="str"/>
+      <x:c r="H50" s="15" t="str"/>
+      <x:c r="I50" s="15" t="str"/>
+      <x:c r="J50" s="15" t="str"/>
+      <x:c r="K50" s="15" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="15" t="str"/>
+      <x:c r="B51" s="15" t="str"/>
+      <x:c r="C51" s="15" t="str"/>
+      <x:c r="D51" s="15" t="str"/>
+      <x:c r="E51" s="15" t="str"/>
+      <x:c r="F51" s="15" t="str"/>
+      <x:c r="G51" s="15" t="str"/>
+      <x:c r="H51" s="15" t="str"/>
+      <x:c r="I51" s="15" t="str"/>
+      <x:c r="J51" s="15" t="str"/>
+      <x:c r="K51" s="15" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="15" t="str"/>
+      <x:c r="B52" s="15" t="str"/>
+      <x:c r="C52" s="15" t="str"/>
+      <x:c r="D52" s="15" t="str"/>
+      <x:c r="E52" s="15" t="str"/>
+      <x:c r="F52" s="15" t="str"/>
+      <x:c r="G52" s="15" t="str"/>
+      <x:c r="H52" s="15" t="str"/>
+      <x:c r="I52" s="15" t="str"/>
+      <x:c r="J52" s="15" t="str"/>
+      <x:c r="K52" s="15" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="15" t="str"/>
+      <x:c r="B53" s="15" t="str"/>
+      <x:c r="C53" s="15" t="str"/>
+      <x:c r="D53" s="15" t="str"/>
+      <x:c r="E53" s="15" t="str"/>
+      <x:c r="F53" s="15" t="str"/>
+      <x:c r="G53" s="15" t="str"/>
+      <x:c r="H53" s="15" t="str"/>
+      <x:c r="I53" s="15" t="str"/>
+      <x:c r="J53" s="15" t="str"/>
+      <x:c r="K53" s="15" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="15" t="str"/>
+      <x:c r="B54" s="15" t="str"/>
+      <x:c r="C54" s="15" t="str"/>
+      <x:c r="D54" s="15" t="str"/>
+      <x:c r="E54" s="15" t="str"/>
+      <x:c r="F54" s="15" t="str"/>
+      <x:c r="G54" s="15" t="str"/>
+      <x:c r="H54" s="15" t="str"/>
+      <x:c r="I54" s="15" t="str"/>
+      <x:c r="J54" s="15" t="str"/>
+      <x:c r="K54" s="15" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="15" t="str"/>
+      <x:c r="B55" s="15" t="str"/>
+      <x:c r="C55" s="15" t="str"/>
+      <x:c r="D55" s="15" t="str"/>
+      <x:c r="E55" s="15" t="str"/>
+      <x:c r="F55" s="15" t="str"/>
+      <x:c r="G55" s="15" t="str"/>
+      <x:c r="H55" s="15" t="str"/>
+      <x:c r="I55" s="15" t="str"/>
+      <x:c r="J55" s="15" t="str"/>
+      <x:c r="K55" s="15" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="15" t="str"/>
+      <x:c r="B56" s="15" t="str"/>
+      <x:c r="C56" s="15" t="str"/>
+      <x:c r="D56" s="15" t="str"/>
+      <x:c r="E56" s="15" t="str"/>
+      <x:c r="F56" s="15" t="str"/>
+      <x:c r="G56" s="15" t="str"/>
+      <x:c r="H56" s="15" t="str"/>
+      <x:c r="I56" s="15" t="str"/>
+      <x:c r="J56" s="15" t="str"/>
+      <x:c r="K56" s="15" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="15" t="str"/>
+      <x:c r="B57" s="15" t="str"/>
+      <x:c r="C57" s="15" t="str"/>
+      <x:c r="D57" s="15" t="str"/>
+      <x:c r="E57" s="15" t="str"/>
+      <x:c r="F57" s="15" t="str"/>
+      <x:c r="G57" s="15" t="str"/>
+      <x:c r="H57" s="15" t="str"/>
+      <x:c r="I57" s="15" t="str"/>
+      <x:c r="J57" s="15" t="str"/>
+      <x:c r="K57" s="15" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="15" t="str"/>
+      <x:c r="B58" s="15" t="str"/>
+      <x:c r="C58" s="15" t="str"/>
+      <x:c r="D58" s="15" t="str"/>
+      <x:c r="E58" s="15" t="str"/>
+      <x:c r="F58" s="15" t="str"/>
+      <x:c r="G58" s="15" t="str"/>
+      <x:c r="H58" s="15" t="str"/>
+      <x:c r="I58" s="15" t="str"/>
+      <x:c r="J58" s="15" t="str"/>
+      <x:c r="K58" s="15" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="15" t="str"/>
+      <x:c r="B59" s="15" t="str"/>
+      <x:c r="C59" s="15" t="str"/>
+      <x:c r="D59" s="15" t="str"/>
+      <x:c r="E59" s="15" t="str"/>
+      <x:c r="F59" s="15" t="str"/>
+      <x:c r="G59" s="15" t="str"/>
+      <x:c r="H59" s="15" t="str"/>
+      <x:c r="I59" s="15" t="str"/>
+      <x:c r="J59" s="15" t="str"/>
+      <x:c r="K59" s="15" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="15" t="str"/>
+      <x:c r="B60" s="15" t="str"/>
+      <x:c r="C60" s="15" t="str"/>
+      <x:c r="D60" s="15" t="str"/>
+      <x:c r="E60" s="15" t="str"/>
+      <x:c r="F60" s="15" t="str"/>
+      <x:c r="G60" s="15" t="str"/>
+      <x:c r="H60" s="15" t="str"/>
+      <x:c r="I60" s="15" t="str"/>
+      <x:c r="J60" s="15" t="str"/>
+      <x:c r="K60" s="15" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="15" t="str"/>
+      <x:c r="B61" s="15" t="str"/>
+      <x:c r="C61" s="15" t="str"/>
+      <x:c r="D61" s="15" t="str"/>
+      <x:c r="E61" s="15" t="str"/>
+      <x:c r="F61" s="15" t="str"/>
+      <x:c r="G61" s="15" t="str"/>
+      <x:c r="H61" s="15" t="str"/>
+      <x:c r="I61" s="15" t="str"/>
+      <x:c r="J61" s="15" t="str"/>
+      <x:c r="K61" s="15" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="15" t="str"/>
+      <x:c r="B62" s="15" t="str"/>
+      <x:c r="C62" s="15" t="str"/>
+      <x:c r="D62" s="15" t="str"/>
+      <x:c r="E62" s="15" t="str"/>
+      <x:c r="F62" s="15" t="str"/>
+      <x:c r="G62" s="15" t="str"/>
+      <x:c r="H62" s="15" t="str"/>
+      <x:c r="I62" s="15" t="str"/>
+      <x:c r="J62" s="15" t="str"/>
+      <x:c r="K62" s="15" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="15" t="str"/>
+      <x:c r="B63" s="15" t="str"/>
+      <x:c r="C63" s="15" t="str"/>
+      <x:c r="D63" s="15" t="str"/>
+      <x:c r="E63" s="15" t="str"/>
+      <x:c r="F63" s="15" t="str"/>
+      <x:c r="G63" s="15" t="str"/>
+      <x:c r="H63" s="15" t="str"/>
+      <x:c r="I63" s="15" t="str"/>
+      <x:c r="J63" s="15" t="str"/>
+      <x:c r="K63" s="15" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="15" t="str"/>
+      <x:c r="B64" s="15" t="str"/>
+      <x:c r="C64" s="15" t="str"/>
+      <x:c r="D64" s="15" t="str"/>
+      <x:c r="E64" s="15" t="str"/>
+      <x:c r="F64" s="15" t="str"/>
+      <x:c r="G64" s="15" t="str"/>
+      <x:c r="H64" s="15" t="str"/>
+      <x:c r="I64" s="15" t="str"/>
+      <x:c r="J64" s="15" t="str"/>
+      <x:c r="K64" s="15" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="15" t="str"/>
+      <x:c r="B65" s="15" t="str"/>
+      <x:c r="C65" s="15" t="str"/>
+      <x:c r="D65" s="15" t="str"/>
+      <x:c r="E65" s="15" t="str"/>
+      <x:c r="F65" s="15" t="str"/>
+      <x:c r="G65" s="15" t="str"/>
+      <x:c r="H65" s="15" t="str"/>
+      <x:c r="I65" s="15" t="str"/>
+      <x:c r="J65" s="15" t="str"/>
+      <x:c r="K65" s="15" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="15" t="str"/>
+      <x:c r="B66" s="15" t="str"/>
+      <x:c r="C66" s="15" t="str"/>
+      <x:c r="D66" s="15" t="str"/>
+      <x:c r="E66" s="15" t="str"/>
+      <x:c r="F66" s="15" t="str"/>
+      <x:c r="G66" s="15" t="str"/>
+      <x:c r="H66" s="15" t="str"/>
+      <x:c r="I66" s="15" t="str"/>
+      <x:c r="J66" s="15" t="str"/>
+      <x:c r="K66" s="15" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="15" t="str"/>
+      <x:c r="B67" s="15" t="str"/>
+      <x:c r="C67" s="15" t="str"/>
+      <x:c r="D67" s="15" t="str"/>
+      <x:c r="E67" s="15" t="str"/>
+      <x:c r="F67" s="15" t="str"/>
+      <x:c r="G67" s="15" t="str"/>
+      <x:c r="H67" s="15" t="str"/>
+      <x:c r="I67" s="15" t="str"/>
+      <x:c r="J67" s="15" t="str"/>
+      <x:c r="K67" s="15" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="15" t="str"/>
+      <x:c r="B68" s="15" t="str"/>
+      <x:c r="C68" s="15" t="str"/>
+      <x:c r="D68" s="15" t="str"/>
+      <x:c r="E68" s="15" t="str"/>
+      <x:c r="F68" s="15" t="str"/>
+      <x:c r="G68" s="15" t="str"/>
+      <x:c r="H68" s="15" t="str"/>
+      <x:c r="I68" s="15" t="str"/>
+      <x:c r="J68" s="15" t="str"/>
+      <x:c r="K68" s="15" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="15" t="str"/>
+      <x:c r="B69" s="15" t="str"/>
+      <x:c r="C69" s="15" t="str"/>
+      <x:c r="D69" s="15" t="str"/>
+      <x:c r="E69" s="15" t="str"/>
+      <x:c r="F69" s="15" t="str"/>
+      <x:c r="G69" s="15" t="str"/>
+      <x:c r="H69" s="15" t="str"/>
+      <x:c r="I69" s="15" t="str"/>
+      <x:c r="J69" s="15" t="str"/>
+      <x:c r="K69" s="15" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="15" t="str"/>
+      <x:c r="B70" s="15" t="str"/>
+      <x:c r="C70" s="15" t="str"/>
+      <x:c r="D70" s="15" t="str"/>
+      <x:c r="E70" s="15" t="str"/>
+      <x:c r="F70" s="15" t="str"/>
+      <x:c r="G70" s="15" t="str"/>
+      <x:c r="H70" s="15" t="str"/>
+      <x:c r="I70" s="15" t="str"/>
+      <x:c r="J70" s="15" t="str"/>
+      <x:c r="K70" s="15" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="15" t="str"/>
+      <x:c r="B71" s="15" t="str"/>
+      <x:c r="C71" s="15" t="str"/>
+      <x:c r="D71" s="15" t="str"/>
+      <x:c r="E71" s="15" t="str"/>
+      <x:c r="F71" s="15" t="str"/>
+      <x:c r="G71" s="15" t="str"/>
+      <x:c r="H71" s="15" t="str"/>
+      <x:c r="I71" s="15" t="str"/>
+      <x:c r="J71" s="15" t="str"/>
+      <x:c r="K71" s="15" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="15" t="str"/>
+      <x:c r="B72" s="15" t="str"/>
+      <x:c r="C72" s="15" t="str"/>
+      <x:c r="D72" s="15" t="str"/>
+      <x:c r="E72" s="15" t="str"/>
+      <x:c r="F72" s="15" t="str"/>
+      <x:c r="G72" s="15" t="str"/>
+      <x:c r="H72" s="15" t="str"/>
+      <x:c r="I72" s="15" t="str"/>
+      <x:c r="J72" s="15" t="str"/>
+      <x:c r="K72" s="15" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="15" t="str"/>
+      <x:c r="B73" s="15" t="str"/>
+      <x:c r="C73" s="15" t="str"/>
+      <x:c r="D73" s="15" t="str"/>
+      <x:c r="E73" s="15" t="str"/>
+      <x:c r="F73" s="15" t="str"/>
+      <x:c r="G73" s="15" t="str"/>
+      <x:c r="H73" s="15" t="str"/>
+      <x:c r="I73" s="15" t="str"/>
+      <x:c r="J73" s="15" t="str"/>
+      <x:c r="K73" s="15" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="15" t="str"/>
+      <x:c r="B74" s="15" t="str"/>
+      <x:c r="C74" s="15" t="str"/>
+      <x:c r="D74" s="15" t="str"/>
+      <x:c r="E74" s="15" t="str"/>
+      <x:c r="F74" s="15" t="str"/>
+      <x:c r="G74" s="15" t="str"/>
+      <x:c r="H74" s="15" t="str"/>
+      <x:c r="I74" s="15" t="str"/>
+      <x:c r="J74" s="15" t="str"/>
+      <x:c r="K74" s="15" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="15" t="str"/>
+      <x:c r="B75" s="15" t="str"/>
+      <x:c r="C75" s="15" t="str"/>
+      <x:c r="D75" s="15" t="str"/>
+      <x:c r="E75" s="15" t="str"/>
+      <x:c r="F75" s="15" t="str"/>
+      <x:c r="G75" s="15" t="str"/>
+      <x:c r="H75" s="15" t="str"/>
+      <x:c r="I75" s="15" t="str"/>
+      <x:c r="J75" s="15" t="str"/>
+      <x:c r="K75" s="15" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="15" t="str"/>
+      <x:c r="B76" s="15" t="str"/>
+      <x:c r="C76" s="15" t="str"/>
+      <x:c r="D76" s="15" t="str"/>
+      <x:c r="E76" s="15" t="str"/>
+      <x:c r="F76" s="15" t="str"/>
+      <x:c r="G76" s="15" t="str"/>
+      <x:c r="H76" s="15" t="str"/>
+      <x:c r="I76" s="15" t="str"/>
+      <x:c r="J76" s="15" t="str"/>
+      <x:c r="K76" s="15" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="15" t="str"/>
+      <x:c r="B77" s="15" t="str"/>
+      <x:c r="C77" s="15" t="str"/>
+      <x:c r="D77" s="15" t="str"/>
+      <x:c r="E77" s="15" t="str"/>
+      <x:c r="F77" s="15" t="str"/>
+      <x:c r="G77" s="15" t="str"/>
+      <x:c r="H77" s="15" t="str"/>
+      <x:c r="I77" s="15" t="str"/>
+      <x:c r="J77" s="15" t="str"/>
+      <x:c r="K77" s="15" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="15" t="str"/>
+      <x:c r="B78" s="15" t="str"/>
+      <x:c r="C78" s="15" t="str"/>
+      <x:c r="D78" s="15" t="str"/>
+      <x:c r="E78" s="15" t="str"/>
+      <x:c r="F78" s="15" t="str"/>
+      <x:c r="G78" s="15" t="str"/>
+      <x:c r="H78" s="15" t="str"/>
+      <x:c r="I78" s="15" t="str"/>
+      <x:c r="J78" s="15" t="str"/>
+      <x:c r="K78" s="15" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="15" t="str"/>
+      <x:c r="B79" s="15" t="str"/>
+      <x:c r="C79" s="15" t="str"/>
+      <x:c r="D79" s="15" t="str"/>
+      <x:c r="E79" s="15" t="str"/>
+      <x:c r="F79" s="15" t="str"/>
+      <x:c r="G79" s="15" t="str"/>
+      <x:c r="H79" s="15" t="str"/>
+      <x:c r="I79" s="15" t="str"/>
+      <x:c r="J79" s="15" t="str"/>
+      <x:c r="K79" s="15" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="15" t="str"/>
+      <x:c r="B80" s="15" t="str"/>
+      <x:c r="C80" s="15" t="str"/>
+      <x:c r="D80" s="15" t="str"/>
+      <x:c r="E80" s="15" t="str"/>
+      <x:c r="F80" s="15" t="str"/>
+      <x:c r="G80" s="15" t="str"/>
+      <x:c r="H80" s="15" t="str"/>
+      <x:c r="I80" s="15" t="str"/>
+      <x:c r="J80" s="15" t="str"/>
+      <x:c r="K80" s="15" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="15" t="str"/>
+      <x:c r="B81" s="15" t="str"/>
+      <x:c r="C81" s="15" t="str"/>
+      <x:c r="D81" s="15" t="str"/>
+      <x:c r="E81" s="15" t="str"/>
+      <x:c r="F81" s="15" t="str"/>
+      <x:c r="G81" s="15" t="str"/>
+      <x:c r="H81" s="15" t="str"/>
+      <x:c r="I81" s="15" t="str"/>
+      <x:c r="J81" s="15" t="str"/>
+      <x:c r="K81" s="15" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="15" t="str"/>
+      <x:c r="B82" s="15" t="str"/>
+      <x:c r="C82" s="15" t="str"/>
+      <x:c r="D82" s="15" t="str"/>
+      <x:c r="E82" s="15" t="str"/>
+      <x:c r="F82" s="15" t="str"/>
+      <x:c r="G82" s="15" t="str"/>
+      <x:c r="H82" s="15" t="str"/>
+      <x:c r="I82" s="15" t="str"/>
+      <x:c r="J82" s="15" t="str"/>
+      <x:c r="K82" s="15" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="15" t="str"/>
+      <x:c r="B83" s="15" t="str"/>
+      <x:c r="C83" s="15" t="str"/>
+      <x:c r="D83" s="15" t="str"/>
+      <x:c r="E83" s="15" t="str"/>
+      <x:c r="F83" s="15" t="str"/>
+      <x:c r="G83" s="15" t="str"/>
+      <x:c r="H83" s="15" t="str"/>
+      <x:c r="I83" s="15" t="str"/>
+      <x:c r="J83" s="15" t="str"/>
+      <x:c r="K83" s="15" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="15" t="str"/>
+      <x:c r="B84" s="15" t="str"/>
+      <x:c r="C84" s="15" t="str"/>
+      <x:c r="D84" s="15" t="str"/>
+      <x:c r="E84" s="15" t="str"/>
+      <x:c r="F84" s="15" t="str"/>
+      <x:c r="G84" s="15" t="str"/>
+      <x:c r="H84" s="15" t="str"/>
+      <x:c r="I84" s="15" t="str"/>
+      <x:c r="J84" s="15" t="str"/>
+      <x:c r="K84" s="15" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="15" t="str"/>
+      <x:c r="B85" s="15" t="str"/>
+      <x:c r="C85" s="15" t="str"/>
+      <x:c r="D85" s="15" t="str"/>
+      <x:c r="E85" s="15" t="str"/>
+      <x:c r="F85" s="15" t="str"/>
+      <x:c r="G85" s="15" t="str"/>
+      <x:c r="H85" s="15" t="str"/>
+      <x:c r="I85" s="15" t="str"/>
+      <x:c r="J85" s="15" t="str"/>
+      <x:c r="K85" s="15" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="15" t="str"/>
+      <x:c r="B86" s="15" t="str"/>
+      <x:c r="C86" s="15" t="str"/>
+      <x:c r="D86" s="15" t="str"/>
+      <x:c r="E86" s="15" t="str"/>
+      <x:c r="F86" s="15" t="str"/>
+      <x:c r="G86" s="15" t="str"/>
+      <x:c r="H86" s="15" t="str"/>
+      <x:c r="I86" s="15" t="str"/>
+      <x:c r="J86" s="15" t="str"/>
+      <x:c r="K86" s="15" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="15" t="str"/>
+      <x:c r="B87" s="15" t="str"/>
+      <x:c r="C87" s="15" t="str"/>
+      <x:c r="D87" s="15" t="str"/>
+      <x:c r="E87" s="15" t="str"/>
+      <x:c r="F87" s="15" t="str"/>
+      <x:c r="G87" s="15" t="str"/>
+      <x:c r="H87" s="15" t="str"/>
+      <x:c r="I87" s="15" t="str"/>
+      <x:c r="J87" s="15" t="str"/>
+      <x:c r="K87" s="15" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="15" t="str"/>
+      <x:c r="B88" s="15" t="str"/>
+      <x:c r="C88" s="15" t="str"/>
+      <x:c r="D88" s="15" t="str"/>
+      <x:c r="E88" s="15" t="str"/>
+      <x:c r="F88" s="15" t="str"/>
+      <x:c r="G88" s="15" t="str"/>
+      <x:c r="H88" s="15" t="str"/>
+      <x:c r="I88" s="15" t="str"/>
+      <x:c r="J88" s="15" t="str"/>
+      <x:c r="K88" s="15" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="15" t="str"/>
+      <x:c r="B89" s="15" t="str"/>
+      <x:c r="C89" s="15" t="str"/>
+      <x:c r="D89" s="15" t="str"/>
+      <x:c r="E89" s="15" t="str"/>
+      <x:c r="F89" s="15" t="str"/>
+      <x:c r="G89" s="15" t="str"/>
+      <x:c r="H89" s="15" t="str"/>
+      <x:c r="I89" s="15" t="str"/>
+      <x:c r="J89" s="15" t="str"/>
+      <x:c r="K89" s="15" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="15" t="str"/>
+      <x:c r="B90" s="15" t="str"/>
+      <x:c r="C90" s="15" t="str"/>
+      <x:c r="D90" s="15" t="str"/>
+      <x:c r="E90" s="15" t="str"/>
+      <x:c r="F90" s="15" t="str"/>
+      <x:c r="G90" s="15" t="str"/>
+      <x:c r="H90" s="15" t="str"/>
+      <x:c r="I90" s="15" t="str"/>
+      <x:c r="J90" s="15" t="str"/>
+      <x:c r="K90" s="15" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="15" t="str"/>
+      <x:c r="B91" s="15" t="str"/>
+      <x:c r="C91" s="15" t="str"/>
+      <x:c r="D91" s="15" t="str"/>
+      <x:c r="E91" s="15" t="str"/>
+      <x:c r="F91" s="15" t="str"/>
+      <x:c r="G91" s="15" t="str"/>
+      <x:c r="H91" s="15" t="str"/>
+      <x:c r="I91" s="15" t="str"/>
+      <x:c r="J91" s="15" t="str"/>
+      <x:c r="K91" s="15" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="15" t="str"/>
+      <x:c r="B92" s="15" t="str"/>
+      <x:c r="C92" s="15" t="str"/>
+      <x:c r="D92" s="15" t="str"/>
+      <x:c r="E92" s="15" t="str"/>
+      <x:c r="F92" s="15" t="str"/>
+      <x:c r="G92" s="15" t="str"/>
+      <x:c r="H92" s="15" t="str"/>
+      <x:c r="I92" s="15" t="str"/>
+      <x:c r="J92" s="15" t="str"/>
+      <x:c r="K92" s="15" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="15" t="str"/>
+      <x:c r="B93" s="15" t="str"/>
+      <x:c r="C93" s="15" t="str"/>
+      <x:c r="D93" s="15" t="str"/>
+      <x:c r="E93" s="15" t="str"/>
+      <x:c r="F93" s="15" t="str"/>
+      <x:c r="G93" s="15" t="str"/>
+      <x:c r="H93" s="15" t="str"/>
+      <x:c r="I93" s="15" t="str"/>
+      <x:c r="J93" s="15" t="str"/>
+      <x:c r="K93" s="15" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="15" t="str"/>
+      <x:c r="B94" s="15" t="str"/>
+      <x:c r="C94" s="15" t="str"/>
+      <x:c r="D94" s="15" t="str"/>
+      <x:c r="E94" s="15" t="str"/>
+      <x:c r="F94" s="15" t="str"/>
+      <x:c r="G94" s="15" t="str"/>
+      <x:c r="H94" s="15" t="str"/>
+      <x:c r="I94" s="15" t="str"/>
+      <x:c r="J94" s="15" t="str"/>
+      <x:c r="K94" s="15" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="15" t="str"/>
+      <x:c r="B95" s="15" t="str"/>
+      <x:c r="C95" s="15" t="str"/>
+      <x:c r="D95" s="15" t="str"/>
+      <x:c r="E95" s="15" t="str"/>
+      <x:c r="F95" s="15" t="str"/>
+      <x:c r="G95" s="15" t="str"/>
+      <x:c r="H95" s="15" t="str"/>
+      <x:c r="I95" s="15" t="str"/>
+      <x:c r="J95" s="15" t="str"/>
+      <x:c r="K95" s="15" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="15" t="str"/>
+      <x:c r="B96" s="15" t="str"/>
+      <x:c r="C96" s="15" t="str"/>
+      <x:c r="D96" s="15" t="str"/>
+      <x:c r="E96" s="15" t="str"/>
+      <x:c r="F96" s="15" t="str"/>
+      <x:c r="G96" s="15" t="str"/>
+      <x:c r="H96" s="15" t="str"/>
+      <x:c r="I96" s="15" t="str"/>
+      <x:c r="J96" s="15" t="str"/>
+      <x:c r="K96" s="15" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="15" t="str"/>
+      <x:c r="B97" s="15" t="str"/>
+      <x:c r="C97" s="15" t="str"/>
+      <x:c r="D97" s="15" t="str"/>
+      <x:c r="E97" s="15" t="str"/>
+      <x:c r="F97" s="15" t="str"/>
+      <x:c r="G97" s="15" t="str"/>
+      <x:c r="H97" s="15" t="str"/>
+      <x:c r="I97" s="15" t="str"/>
+      <x:c r="J97" s="15" t="str"/>
+      <x:c r="K97" s="15" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="15" t="str"/>
+      <x:c r="B98" s="15" t="str"/>
+      <x:c r="C98" s="15" t="str"/>
+      <x:c r="D98" s="15" t="str"/>
+      <x:c r="E98" s="15" t="str"/>
+      <x:c r="F98" s="15" t="str"/>
+      <x:c r="G98" s="15" t="str"/>
+      <x:c r="H98" s="15" t="str"/>
+      <x:c r="I98" s="15" t="str"/>
+      <x:c r="J98" s="15" t="str"/>
+      <x:c r="K98" s="15" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="15" t="str"/>
+      <x:c r="B99" s="15" t="str"/>
+      <x:c r="C99" s="15" t="str"/>
+      <x:c r="D99" s="15" t="str"/>
+      <x:c r="E99" s="15" t="str"/>
+      <x:c r="F99" s="15" t="str"/>
+      <x:c r="G99" s="15" t="str"/>
+      <x:c r="H99" s="15" t="str"/>
+      <x:c r="I99" s="15" t="str"/>
+      <x:c r="J99" s="15" t="str"/>
+      <x:c r="K99" s="15" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="15" t="str"/>
+      <x:c r="B100" s="15" t="str"/>
+      <x:c r="C100" s="15" t="str"/>
+      <x:c r="D100" s="15" t="str"/>
+      <x:c r="E100" s="15" t="str"/>
+      <x:c r="F100" s="15" t="str"/>
+      <x:c r="G100" s="15" t="str"/>
+      <x:c r="H100" s="15" t="str"/>
+      <x:c r="I100" s="15" t="str"/>
+      <x:c r="J100" s="15" t="str"/>
+      <x:c r="K100" s="15" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="15" t="str"/>
+      <x:c r="B101" s="15" t="str"/>
+      <x:c r="C101" s="15" t="str"/>
+      <x:c r="D101" s="15" t="str"/>
+      <x:c r="E101" s="15" t="str"/>
+      <x:c r="F101" s="15" t="str"/>
+      <x:c r="G101" s="15" t="str"/>
+      <x:c r="H101" s="15" t="str"/>
+      <x:c r="I101" s="15" t="str"/>
+      <x:c r="J101" s="15" t="str"/>
+      <x:c r="K101" s="15" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="15" t="str"/>
+      <x:c r="B102" s="15" t="str"/>
+      <x:c r="C102" s="15" t="str"/>
+      <x:c r="D102" s="15" t="str"/>
+      <x:c r="E102" s="15" t="str"/>
+      <x:c r="F102" s="15" t="str"/>
+      <x:c r="G102" s="15" t="str"/>
+      <x:c r="H102" s="15" t="str"/>
+      <x:c r="I102" s="15" t="str"/>
+      <x:c r="J102" s="15" t="str"/>
+      <x:c r="K102" s="15" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="E2:E102">
+      <x:formula1>"v5.5,v5,v4.5+,v4.5-all"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F102">
+      <x:formula1>"不指定,女声,男声"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I102">
+      <x:formula1>"1,2,3"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K2:K102">
+      <x:formula1>"是,否"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01fe6b97e9894277"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
